--- a/Result/profitability/5905.xlsx
+++ b/Result/profitability/5905.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1525</v>
+        <v>-0.12875</v>
       </c>
       <c r="N2" t="n">
-        <v>65.70375</v>
+        <v>59.525</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,25 +780,25 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.14</v>
+        <v>-0.08374999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>63.0125</v>
+        <v>55.43</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09749999999999999</v>
+        <v>-0.06125</v>
       </c>
       <c r="N4" t="n">
-        <v>59.6725</v>
+        <v>53.37</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.13375</v>
+        <v>-0.09125</v>
       </c>
       <c r="N5" t="n">
-        <v>57.6675</v>
+        <v>51.5925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.21</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.13625</v>
+        <v>-0.11375</v>
       </c>
       <c r="N6" t="n">
-        <v>55.55</v>
+        <v>49.34</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.16125</v>
+        <v>-0.10875</v>
       </c>
       <c r="N7" t="n">
-        <v>53.835</v>
+        <v>47.2725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.16125</v>
+        <v>-0.13125</v>
       </c>
       <c r="N8" t="n">
-        <v>51.61625</v>
+        <v>49.945</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E75" t="n">
+        <v>295</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>40</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>42</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.11375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>63.2625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-13.37</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3708737864077669</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.789473684210526</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-48.6</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6818181818181819</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
